--- a/consulting_forms/025_home_buyer_consultation_questionnaire_form--consulting_forms.xlsx
+++ b/consulting_forms/025_home_buyer_consultation_questionnaire_form--consulting_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1213,7 +1213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:C59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1773,29 +1773,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>townhouse</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>home_building_type_choices</t>
+          <t>home_age_of_building_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>less_than_5</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Less than 5</t>
         </is>
       </c>
     </row>
@@ -1807,12 +1807,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>less_than_5</t>
+          <t>5-10</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Less than 5</t>
+          <t>5-10</t>
         </is>
       </c>
     </row>
@@ -1824,12 +1824,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5-10</t>
+          <t>10-20</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>5-10</t>
+          <t>10-20</t>
         </is>
       </c>
     </row>
@@ -1841,29 +1841,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>10-20</t>
+          <t>more_than_20</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>10-20</t>
+          <t>More than 20</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>home_age_of_building_choices</t>
+          <t>home_neighborhood_features_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>more_than_20</t>
+          <t>park</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>More than 20</t>
+          <t>Park</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>park</t>
+          <t>school</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Park</t>
+          <t>School</t>
         </is>
       </c>
     </row>
@@ -1892,12 +1892,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>school</t>
+          <t>grocery</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>School</t>
+          <t>Grocery</t>
         </is>
       </c>
     </row>
@@ -1909,12 +1909,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>grocery</t>
+          <t>highway</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Grocery</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -1926,12 +1926,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>highway</t>
+          <t>highway-5min</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Highway-5min</t>
         </is>
       </c>
     </row>
@@ -1943,12 +1943,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>highway-5min</t>
+          <t>close_to_public_transport</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Highway-5min</t>
+          <t>Close to public transport</t>
         </is>
       </c>
     </row>
@@ -1960,12 +1960,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>close_to_public_transport</t>
+          <t>view</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Close to public transport</t>
+          <t>View</t>
         </is>
       </c>
     </row>
@@ -1977,29 +1977,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>view</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>home_neighborhood_features_choices</t>
+          <t>preferred_commute_time_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>less_than_10</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Less than 10</t>
         </is>
       </c>
     </row>
@@ -2011,12 +2011,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>less_than_10</t>
+          <t>10-20</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Less than 10</t>
+          <t>10-20</t>
         </is>
       </c>
     </row>
@@ -2028,12 +2028,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>10-20</t>
+          <t>20-30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>10-20</t>
+          <t>20-30</t>
         </is>
       </c>
     </row>
@@ -2045,12 +2045,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>20-30</t>
+          <t>30-40</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>20-30</t>
+          <t>30-40</t>
         </is>
       </c>
     </row>
@@ -2062,29 +2062,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>30-40</t>
+          <t>more_than_40</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>30-40</t>
+          <t>More than 40</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>preferred_commute_time_choices</t>
+          <t>preferred_commute_type_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>more_than_40</t>
+          <t>car</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>More than 40</t>
+          <t>Car</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>public_transit</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Public Transit</t>
         </is>
       </c>
     </row>
@@ -2113,12 +2113,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>public_transit</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Public Transit</t>
+          <t>Walk</t>
         </is>
       </c>
     </row>
@@ -2130,29 +2130,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>bike</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Walk</t>
+          <t>Bike</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>preferred_commute_type_choices</t>
+          <t>preferred_work_hours_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>bike</t>
+          <t>less_than_4</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bike</t>
+          <t>Less than 4</t>
         </is>
       </c>
     </row>
@@ -2164,12 +2164,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>less_than_4</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Less than 4</t>
+          <t>4-6</t>
         </is>
       </c>
     </row>
@@ -2181,12 +2181,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>6-8</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>6-8</t>
         </is>
       </c>
     </row>
@@ -2198,12 +2198,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>6-8</t>
+          <t>8-12</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>6-8</t>
+          <t>8-12</t>
         </is>
       </c>
     </row>
@@ -2215,27 +2215,10 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>8-12</t>
+          <t>more_than_12</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
-        <is>
-          <t>8-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>preferred_work_hours_choices</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>more_than_12</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
         <is>
           <t>More than 12</t>
         </is>
